--- a/Excel/立绘表.xlsx
+++ b/Excel/立绘表.xlsx
@@ -1,42 +1,187 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C2654F9-C940-4C56-83E2-5D8A34E702D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="35505" yWindow="1995" windowWidth="10905" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="立绘" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="立绘" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
+  <si>
+    <t>立绘ID</t>
+  </si>
+  <si>
+    <t>资源路径</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>portraitId</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>crow_平静</t>
+  </si>
+  <si>
+    <t>OutGameUI/Guests/crow</t>
+  </si>
+  <si>
+    <t>fox_平静</t>
+  </si>
+  <si>
+    <t>OutGameUI/Guests/fox</t>
+  </si>
+  <si>
+    <t>hedgehog_平静</t>
+  </si>
+  <si>
+    <t>OutGameUI/Guests/hedgehog</t>
+  </si>
+  <si>
+    <t>rabbit_平静</t>
+  </si>
+  <si>
+    <t>OutGameUI/Guests/rabbit</t>
+  </si>
+  <si>
+    <t>鸦族_默认脸</t>
+  </si>
+  <si>
+    <t>crow_02</t>
+  </si>
+  <si>
+    <t>crow_03</t>
+  </si>
+  <si>
+    <t>crow_04</t>
+  </si>
+  <si>
+    <t>crow_05</t>
+  </si>
+  <si>
+    <t>狐族_默认脸</t>
+  </si>
+  <si>
+    <t>fox_02</t>
+  </si>
+  <si>
+    <t>fox_03</t>
+  </si>
+  <si>
+    <t>fox_04</t>
+  </si>
+  <si>
+    <t>fox_05</t>
+  </si>
+  <si>
+    <t>猬族_默认脸</t>
+  </si>
+  <si>
+    <t>hedgehog_02</t>
+  </si>
+  <si>
+    <t>hedgehog_03</t>
+  </si>
+  <si>
+    <t>hedgehog_04</t>
+  </si>
+  <si>
+    <t>hedgehog_05</t>
+  </si>
+  <si>
+    <t>兔族_默认脸</t>
+  </si>
+  <si>
+    <t>rabbit_02</t>
+  </si>
+  <si>
+    <t>rabbit_03</t>
+  </si>
+  <si>
+    <t>rabbit_04</t>
+  </si>
+  <si>
+    <t>rabbit_05</t>
+  </si>
+  <si>
+    <t>OutGameUI/Guests/crow02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutGameUI/Guests/fox02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutGameUI/Guests/hedgehog02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutGameUI/Guests/rabbit02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <i val="1"/>
+      <i/>
+      <sz val="9"/>
       <color rgb="FF808080"/>
-      <sz val="9"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -44,10 +189,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E2F3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,87 +207,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -423,122 +533,260 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>立绘ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>资源路径</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>portraitId</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>path</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>crow_平静</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>OutGameUI/Guests/crow</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>鸦族默认脸</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>fox_平静</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>OutGameUI/Guests/fox</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>狐族默认脸</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>hedgehog_平静</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>OutGameUI/Guests/hedgehog</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>猬族默认脸</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>rabbit_平静</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>OutGameUI/Guests/rabbit</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>兔族默认脸</t>
-        </is>
+    <row r="1" spans="1:3" ht="15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="16.5">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="16.5">
+      <c r="A4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="16.5">
+      <c r="A5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="16.5">
+      <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="16.5">
+      <c r="A7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="16.5">
+      <c r="A8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="16.5">
+      <c r="A9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="16.5">
+      <c r="A10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="16.5">
+      <c r="A11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="16.5">
+      <c r="A12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="16.5">
+      <c r="A13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="16.5">
+      <c r="A14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="16.5">
+      <c r="A15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="16.5">
+      <c r="A16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="16.5">
+      <c r="A17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="16.5">
+      <c r="A18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="16.5">
+      <c r="A19" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="16.5">
+      <c r="A20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="16.5">
+      <c r="A21" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="16.5">
+      <c r="A22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Excel/立绘表.xlsx
+++ b/Excel/立绘表.xlsx
@@ -1,59 +1,232 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599D573F-1F31-4B91-94E2-3239457BE7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="35505" yWindow="1995" windowWidth="10905" windowHeight="13260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="5160" yWindow="1065" windowWidth="16065" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="立绘" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="立绘" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="47">
+  <si>
+    <t>立绘ID</t>
+  </si>
+  <si>
+    <t>资源路径</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>portraitId</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>rabbit_平静</t>
+  </si>
+  <si>
+    <t>OutGameUI/Portraits/rabbit</t>
+  </si>
+  <si>
+    <t>兔族_白兔·蓝斗篷，最能等</t>
+  </si>
+  <si>
+    <t>OutGameUI/Portraits/goat</t>
+  </si>
+  <si>
+    <t>羊族_白山羊·捧盆栽</t>
+  </si>
+  <si>
+    <t>OutGameUI/Portraits/wolf</t>
+  </si>
+  <si>
+    <t>狼族_白狼·白西装，急性子</t>
+  </si>
+  <si>
+    <t>leopard_平静</t>
+  </si>
+  <si>
+    <t>OutGameUI/Portraits/leopard</t>
+  </si>
+  <si>
+    <t>豹族_豹·棒球帽</t>
+  </si>
+  <si>
+    <t>OutGameUI/Portraits/cheetah</t>
+  </si>
+  <si>
+    <t>猎豹族_猎豹·棒球服，坐不住</t>
+  </si>
+  <si>
+    <t>OutGameUI/Portraits/ox</t>
+  </si>
+  <si>
+    <t>牛族_褐牛·毛线帽，慢性子</t>
+  </si>
+  <si>
+    <t>cat_平静</t>
+  </si>
+  <si>
+    <t>OutGameUI/Portraits/cat</t>
+  </si>
+  <si>
+    <t>猫族_黑猫·警官</t>
+  </si>
+  <si>
+    <t>OutGameUI/Portraits/yak</t>
+  </si>
+  <si>
+    <t>牦牛族_白牦牛·蓝衬衫</t>
+  </si>
+  <si>
+    <t>rabbit_伤心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rabbit_开心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平静脸预占</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goat_平静</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goat_开心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goat_伤心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wolf_平静</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wolf_开心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wolf_伤心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leopard_开心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leopard_伤心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cheetah_伤心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cheetah_开心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cheetah_平静</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ox_平静</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ox_开心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ox_伤心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cat_伤心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cat_开心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yak_平静</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yak_开心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yak_伤心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
       <name val="微软雅黑"/>
       <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF808080"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -61,12 +234,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E2F3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -98,85 +265,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -464,203 +571,345 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>立绘ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>资源路径</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>portraitId</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>path</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>rabbit_平静</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>OutGameUI/Portraits/rabbit</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>兔族_白兔·蓝斗篷，最能等</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16.5" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>goat_平静</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>OutGameUI/Portraits/goat</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>羊族_白山羊·捧盆栽</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16.5" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>wolf_平静</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>OutGameUI/Portraits/wolf</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>狼族_白狼·白西装，急性子</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>leopard_平静</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>OutGameUI/Portraits/leopard</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>豹族_豹·棒球帽</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>cheetah_平静</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>OutGameUI/Portraits/cheetah</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>猎豹族_猎豹·棒球服，坐不住</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>ox_平静</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>OutGameUI/Portraits/ox</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>牛族_褐牛·毛线帽，慢性子</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>cat_平静</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>OutGameUI/Portraits/cat</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>猫族_黑猫·警官</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>yak_平静</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>OutGameUI/Portraits/yak</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>牦牛族_白牦牛·蓝衬衫</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16.5" customHeight="1"/>
-    <row r="12" ht="16.5" customHeight="1"/>
-    <row r="13" ht="16.5" customHeight="1"/>
-    <row r="14" ht="16.5" customHeight="1"/>
-    <row r="15" ht="16.5" customHeight="1"/>
-    <row r="16" ht="16.5" customHeight="1"/>
-    <row r="17" ht="16.5" customHeight="1"/>
-    <row r="18" ht="16.5" customHeight="1"/>
-    <row r="19" ht="16.5" customHeight="1"/>
-    <row r="20" ht="16.5" customHeight="1"/>
-    <row r="21" ht="16.5" customHeight="1"/>
-    <row r="22" ht="16.5" customHeight="1"/>
+    <row r="1" spans="1:3" ht="15" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="16.5" customHeight="1"/>
+    <row r="31" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A32" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="16.5" customHeight="1">
+      <c r="A33" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="16.5" customHeight="1"/>
+    <row r="35" spans="1:3" ht="16.5" customHeight="1"/>
+    <row r="36" spans="1:3" ht="16.5" customHeight="1"/>
+    <row r="37" spans="1:3" ht="16.5" customHeight="1"/>
+    <row r="38" spans="1:3" ht="16.5" customHeight="1"/>
+    <row r="39" spans="1:3" ht="16.5" customHeight="1"/>
+    <row r="40" spans="1:3" ht="16.5" customHeight="1"/>
+    <row r="41" spans="1:3" ht="16.5" customHeight="1"/>
+    <row r="42" spans="1:3" ht="16.5" customHeight="1"/>
+    <row r="43" spans="1:3" ht="16.5" customHeight="1"/>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Excel/立绘表.xlsx
+++ b/Excel/立绘表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinxinhe\Documents\2026MasterHouse\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599D573F-1F31-4B91-94E2-3239457BE7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF258AB-DFF7-40E7-8E21-20BD667E301D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5160" yWindow="1065" windowWidth="16065" windowHeight="13260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="立绘" sheetId="1" r:id="rId1"/>
@@ -64,124 +64,126 @@
     <t>leopard_平静</t>
   </si>
   <si>
+    <t>豹族_豹·棒球帽</t>
+  </si>
+  <si>
+    <t>猎豹族_猎豹·棒球服，坐不住</t>
+  </si>
+  <si>
+    <t>OutGameUI/Portraits/ox</t>
+  </si>
+  <si>
+    <t>牛族_褐牛·毛线帽，慢性子</t>
+  </si>
+  <si>
+    <t>cat_平静</t>
+  </si>
+  <si>
+    <t>OutGameUI/Portraits/cat</t>
+  </si>
+  <si>
+    <t>猫族_黑猫·警官</t>
+  </si>
+  <si>
+    <t>OutGameUI/Portraits/yak</t>
+  </si>
+  <si>
+    <t>牦牛族_白牦牛·蓝衬衫</t>
+  </si>
+  <si>
+    <t>rabbit_伤心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rabbit_开心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平静脸预占</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goat_平静</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goat_开心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goat_伤心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wolf_平静</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wolf_开心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wolf_伤心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leopard_开心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leopard_伤心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cheetah_伤心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cheetah_开心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cheetah_平静</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ox_平静</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ox_开心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ox_伤心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cat_伤心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cat_开心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yak_平静</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yak_开心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yak_伤心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OutGameUI/Portraits/cheetah</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>OutGameUI/Portraits/leopard</t>
-  </si>
-  <si>
-    <t>豹族_豹·棒球帽</t>
-  </si>
-  <si>
-    <t>OutGameUI/Portraits/cheetah</t>
-  </si>
-  <si>
-    <t>猎豹族_猎豹·棒球服，坐不住</t>
-  </si>
-  <si>
-    <t>OutGameUI/Portraits/ox</t>
-  </si>
-  <si>
-    <t>牛族_褐牛·毛线帽，慢性子</t>
-  </si>
-  <si>
-    <t>cat_平静</t>
-  </si>
-  <si>
-    <t>OutGameUI/Portraits/cat</t>
-  </si>
-  <si>
-    <t>猫族_黑猫·警官</t>
-  </si>
-  <si>
-    <t>OutGameUI/Portraits/yak</t>
-  </si>
-  <si>
-    <t>牦牛族_白牦牛·蓝衬衫</t>
-  </si>
-  <si>
-    <t>rabbit_伤心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rabbit_开心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>平静脸预占</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>goat_平静</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>goat_开心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>goat_伤心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wolf_平静</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wolf_开心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wolf_伤心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>leopard_开心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>leopard_伤心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cheetah_伤心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cheetah_开心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cheetah_平静</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ox_平静</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ox_开心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ox_伤心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cat_伤心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cat_开心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>yak_平静</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>yak_开心</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>yak_伤心</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -615,24 +617,24 @@
     </row>
     <row r="4" spans="1:3" ht="16.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="16.5" customHeight="1">
@@ -642,7 +644,7 @@
     </row>
     <row r="7" spans="1:3" ht="16.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>9</v>
@@ -653,24 +655,24 @@
     </row>
     <row r="8" spans="1:3" ht="16.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16.5" customHeight="1">
@@ -680,7 +682,7 @@
     </row>
     <row r="11" spans="1:3" ht="16.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
@@ -691,24 +693,24 @@
     </row>
     <row r="12" spans="1:3" ht="16.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="16.5" customHeight="1">
@@ -721,32 +723,32 @@
         <v>13</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="16.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="16.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="16.5" customHeight="1">
@@ -756,35 +758,35 @@
     </row>
     <row r="19" spans="1:3" ht="16.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="16.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="16.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="16.5" customHeight="1">
@@ -794,35 +796,35 @@
     </row>
     <row r="23" spans="1:3" ht="16.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="16.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="16.5" customHeight="1">
@@ -832,69 +834,69 @@
     </row>
     <row r="27" spans="1:3" ht="16.5" customHeight="1">
       <c r="A27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="16.5" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="16.5" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="16.5" customHeight="1"/>
     <row r="31" spans="1:3" ht="16.5" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="16.5" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="16.5" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="16.5" customHeight="1"/>
